--- a/docs/HeatTransforerSequence-2026.xlsx
+++ b/docs/HeatTransforerSequence-2026.xlsx
@@ -5,20 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s2463492\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iwheard\Documents\0000-labview\000-research\adsorption_rig_process_lab\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D3FBAD-534A-4FB7-8CCA-BDF2C51EF9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23688A58-6CAF-4F91-AE08-18DC03601C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="30990" yWindow="4530" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AutomaticMode" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -33,7 +42,7 @@
     <author>Amir Zivariravan</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{66517117-66CF-4058-B227-71759EA261E8}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{66517117-66CF-4058-B227-71759EA261E8}">
       <text>
         <r>
           <rPr>
@@ -57,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{9D854A6E-1155-417E-9AF6-F0948A0861E6}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{9D854A6E-1155-417E-9AF6-F0948A0861E6}">
       <text>
         <r>
           <rPr>
@@ -81,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{70FEE009-D02A-4DBF-9ACA-F0A2AD3F2D63}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{70FEE009-D02A-4DBF-9ACA-F0A2AD3F2D63}">
       <text>
         <r>
           <rPr>
@@ -105,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{A6AAB9C0-F27B-498D-847E-38030EC78924}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{A6AAB9C0-F27B-498D-847E-38030EC78924}">
       <text>
         <r>
           <rPr>
@@ -129,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{BE3856A2-CDB5-43F4-83BC-0A28C5799099}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{BE3856A2-CDB5-43F4-83BC-0A28C5799099}">
       <text>
         <r>
           <rPr>
@@ -153,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{7F8B6B35-69DC-481C-8FF7-8AA8EC104137}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{7F8B6B35-69DC-481C-8FF7-8AA8EC104137}">
       <text>
         <r>
           <rPr>
@@ -177,7 +186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{762939B9-F799-4E25-9E4D-C133DEAE7CD4}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{762939B9-F799-4E25-9E4D-C133DEAE7CD4}">
       <text>
         <r>
           <rPr>
@@ -206,7 +215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="97">
   <si>
     <t>V1</t>
   </si>
@@ -473,6 +482,30 @@
   </si>
   <si>
     <t>X = closed. O = open</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>isos1</t>
+  </si>
+  <si>
+    <t>ads1</t>
+  </si>
+  <si>
+    <t>HRA</t>
+  </si>
+  <si>
+    <t>Isos2</t>
+  </si>
+  <si>
+    <t>Ads2</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>Receirc</t>
   </si>
 </sst>
 </file>
@@ -549,13 +582,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -582,14 +618,14 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>558730</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>171610</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>316105</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>154084</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>154083</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -626,13 +662,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>476251</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>74839</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>394608</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -708,13 +744,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>132071</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>147277</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>244127</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>225718</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -785,13 +821,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>79241</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>198505</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>101654</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1137,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1150,456 +1186,450 @@
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E1" s="4" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E1" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E2" s="2" t="s">
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E2" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="E5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="E6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="E7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="E9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="E10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="E13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="E14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="E15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>23</v>
@@ -1611,7 +1641,7 @@
         <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>86</v>
@@ -1620,7 +1650,7 @@
         <v>86</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>86</v>
@@ -1628,253 +1658,285 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>41</v>
+      <c r="E20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>52</v>
       </c>
     </row>
